--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-core-name.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-core-name.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>CDA - name</t>
+    <t xml:space="preserve">CDA - Name </t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:49:50+00:00</t>
+    <t>2025-09-03T12:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>L'élément de l'en-tête du CDA name correspond au nom d'une personne physique.</t>
+    <t>L'élément de l'en-tête du CDA  correspond au nom d'une personne physique.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-core-name.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-core-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
